--- a/Circuito/dom32-touch-Materiales.xlsx
+++ b/Circuito/dom32-touch-Materiales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2708d86aa79f336/Documentos/Git/dom32-touch/Circuito/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{AB4AD6D3-1ADD-4753-B268-0A87D7AF4A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5030820C-44E4-4EBF-A19D-C07317CACCAD}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{AB4AD6D3-1ADD-4753-B268-0A87D7AF4A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{714310BF-C0C7-45BB-A7C7-31534E157476}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="1755" windowWidth="20910" windowHeight="12660" xr2:uid="{954617B2-1595-4720-8356-B08278AFF7FB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{954617B2-1595-4720-8356-B08278AFF7FB}"/>
   </bookViews>
   <sheets>
     <sheet name="dom32-touch-Materiales" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Identificador</t>
   </si>
@@ -164,6 +164,15 @@
   </si>
   <si>
     <t>PIC32MM0256GPM028-I-SS</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>AFY240320B0-2.4N6NTM-R</t>
+  </si>
+  <si>
+    <t>https://www.orientdisplay.com/products/afy240320b0-2-4n6ntm-r-2-4-tft-370-nits/</t>
   </si>
 </sst>
 </file>
@@ -1024,15 +1033,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16E2AA9-FDD7-43B1-89C6-37BF40832499}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1043,7 +1052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1054,7 +1063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1065,7 +1074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1076,7 +1085,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1087,7 +1096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -1098,7 +1107,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1109,7 +1118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1120,7 +1129,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1131,7 +1140,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -1142,7 +1151,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -1153,7 +1162,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1164,7 +1173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1175,7 +1184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -1186,7 +1195,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1197,7 +1206,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1208,7 +1217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1219,7 +1228,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1230,7 +1239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1241,7 +1250,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1252,7 +1261,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1263,7 +1272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -1274,7 +1283,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -1283,6 +1292,20 @@
       </c>
       <c r="C23" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Circuito/dom32-touch-Materiales.xlsx
+++ b/Circuito/dom32-touch-Materiales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2708d86aa79f336/Documentos/Git/dom32-touch/Circuito/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{AB4AD6D3-1ADD-4753-B268-0A87D7AF4A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{714310BF-C0C7-45BB-A7C7-31534E157476}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{AB4AD6D3-1ADD-4753-B268-0A87D7AF4A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F86ECFD3-AD07-4B0C-8C82-4A8ABEB887D3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{954617B2-1595-4720-8356-B08278AFF7FB}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="dom32-touch-Materiales" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'dom32-touch-Materiales'!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'dom32-touch-Materiales'!$B$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -37,9 +37,6 @@
     <t>D4,D1,D3</t>
   </si>
   <si>
-    <t>3191-M7CT-ND</t>
-  </si>
-  <si>
     <t>J4</t>
   </si>
   <si>
@@ -173,6 +170,9 @@
   </si>
   <si>
     <t>https://www.orientdisplay.com/products/afy240320b0-2-4n6ntm-r-2-4-tft-370-nits/</t>
+  </si>
+  <si>
+    <t>3372-M7TR-ND</t>
   </si>
 </sst>
 </file>
@@ -496,7 +496,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -611,6 +611,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -656,8 +671,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -714,6 +730,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1033,285 +1053,334 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16E2AA9-FDD7-43B1-89C6-37BF40832499}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.81640625" customWidth="1"/>
+    <col min="2" max="2" width="41.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C15" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="E24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D24" t="s">
-        <v>49</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{A16E2AA9-FDD7-43B1-89C6-37BF40832499}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C23">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="B1:D1" xr:uid="{A16E2AA9-FDD7-43B1-89C6-37BF40832499}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D23">
+      <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
